--- a/data/trans_camb/IP09-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.5731171923401113</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.595256029258646</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.760080073115496</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.850887166481828</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.125889443451772</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-4.049052791043883</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-21.09570826650943</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-31.9465046202276</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-21.07273963001642</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-32.08729583357491</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-15.11536524157751</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-23.01905354118675</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>22.48138560008566</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>25.45069893721093</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>25.4027185914366</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25.50200299945962</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>17.54624725164587</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>18.20706350514879</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.01226471129370572</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.03413848842766834</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.1069567822367652</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1948758623608011</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0271862578520011</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.09777033959586906</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.414054775215734</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5947804776204837</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.4879963471865163</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8003941985560874</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3160349970230941</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4994904582312075</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.5988263232044165</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.6155715048637832</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.025299767696185</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.042514833914509</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4983234344838657</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5755049705727432</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>25.65133366565918</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9578065697262883</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.377176058886034</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.346753546812412</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>16.29785528120544</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.523878454147754</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>0.6875840289144437</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-22.49336231972604</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-20.24043707560464</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-33.8396608007405</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.793592838720426</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-22.48363345967945</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>52.24675923355224</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>22.24513472267999</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>30.89703230016569</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.38458015318508</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>34.73020565068586</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>14.33301716766292</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.9410142313345111</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.03513694939708963</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1035655337097424</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1738267873792602</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4964428473261068</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.07687891348053809</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>0.02755186587746545</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.6285149338934402</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3772551369731734</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6517856179489351</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07332597875619519</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5617077943346318</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>2.925769969576846</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.044864975329409</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.23951795694551</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.6781245462493621</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.384861673942791</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4945373134014634</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>27.53145086630616</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.626992108204648</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>9.571812685145058</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>15.5487423978136</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>20.22392067956626</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7.734535485466782</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.876665461061421</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-23.97316738519433</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-23.62917792038889</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.17076250590271</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.764636323262428</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-10.68959216724013</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>54.41973593576921</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>29.40661714440742</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>39.75413780535324</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>43.0416938801878</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>42.12453922766156</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>26.18506477375811</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>1.26616164459025</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.1208144337979916</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.4014158152636049</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.6520720067609154</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.8759077044793417</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.3349864415327858</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.2930298597476224</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.6392475507127163</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7441458781001949</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.3690706377919617</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.06744726046886329</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3571539032359781</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>7.619444537742929</v>
+      </c>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="n">
+        <v>3.177251059806952</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3.540131754652473</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>3.334367544855556</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.096203410669545</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1078,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>9.798926468685865</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>16.7814835887153</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>16.27977495840291</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.331584506845799</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>11.06267261641055</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>10.35345690317822</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1104,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-23.07536032768306</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-9.610755937697673</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-38.11414879827413</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-30.19325536141777</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-15.2536631569037</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-8.747772580348071</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1130,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>49.52346196719816</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>45.17982861285579</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>81.93879989361163</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>27.822383357669</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>44.09418275871403</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>30.1854254353043</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1156,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.4235442104447417</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.7253549906091932</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.6824270253995181</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.09773699473978942</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.4728969763172881</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.442580073885704</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1182,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3157329633987019</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>-0.6919464854798587</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5914725955298182</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.2893959490228754</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1206,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>5.2232025801477</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.856763817389552</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
+        <v>4.36177796053397</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>3.463443556366614</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.371691816310695</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1234,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>12.74647964788013</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.444444485810865</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>7.299401830863045</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.5608634227047438</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>10.12753257842929</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.677630763419902</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1260,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-0.5030142949970782</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-15.569270818025</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-7.956135631913064</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-13.52214410217777</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.7920056514308431</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-11.71755255449792</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1286,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>26.73371891643179</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>10.19449351552662</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>22.29161686744829</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>12.68013448813853</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>20.89890207984831</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>7.645695246135212</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1312,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.3738788578794931</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.07170027629211227</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.2166230542589642</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.01664464437821928</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.2985998005139197</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.04946320413327073</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1338,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.02101158616552687</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.4142991342521028</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2038411640352487</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3547526347897705</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.02684773489349636</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3070777830717618</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1364,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.8893542947616911</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3566005605035608</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.7952475451028053</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.4629546207067387</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.7318363895932407</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.2592567892479781</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1392,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
